--- a/korjournal.xlsx
+++ b/korjournal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I272"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11364,6 +11364,45 @@
       </c>
       <c r="I272" t="inlineStr"/>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>105</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Ängsmarksvägen 8B, 749 44 Enköping</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>152</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resa från särbo till jobbet </t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/korjournal.xlsx
+++ b/korjournal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11403,6 +11403,45 @@
       </c>
       <c r="I273" t="inlineStr"/>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>105</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Ängsmarksvägen 8B, 749 44 Enköping</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>152</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Resa från jobbet till särbo</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/korjournal.xlsx
+++ b/korjournal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I274"/>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11442,6 +11442,45 @@
       </c>
       <c r="I274" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>105</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Ängsmarksvägen 8B, 749 44 Enköping</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>152</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Resa till jobbet från särbo</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/korjournal.xlsx
+++ b/korjournal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I275"/>
+  <dimension ref="A1:I276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11481,6 +11481,45 @@
       </c>
       <c r="I275" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>105</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Ängsmarksvägen 8B, 749 44 Enköping</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>152</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Resa från jobbet till särbo</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/korjournal.xlsx
+++ b/korjournal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I276"/>
+  <dimension ref="A1:I278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11520,6 +11520,84 @@
       </c>
       <c r="I276" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>01:07</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>37</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Bruksgatan 4D, 78474 Borlänge</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Resa till jobbet</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>37</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Bruksgatan 4D, 78474 Borlänge</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Resa hem från jobbet</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/korjournal.xlsx
+++ b/korjournal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I278"/>
+  <dimension ref="A1:I280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11598,6 +11598,84 @@
       </c>
       <c r="I278" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>01:07</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>37</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Bruksgatan 4D, 78474 Borlänge</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Resa till jobbet</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>37</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Kajvägen 13 Parking, Ludvika</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Bruksgatan 4D, 78474 Borlänge</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Resa hem från jobbet</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
